--- a/Employee_Reports_wi52/Ernesto JR Leona Campana Q0424.xlsx
+++ b/Employee_Reports_wi52/Ernesto JR Leona Campana Q0424.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-151</v>
+        <v>-159</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-152</v>
+        <v>-160</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
